--- a/research/results/Model_Results/optimized_model_results.xlsx
+++ b/research/results/Model_Results/optimized_model_results.xlsx
@@ -465,26 +465,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6440677966101694</v>
+        <v>0.652542372881356</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7966101694915254</v>
+        <v>0.8050847457627118</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7372881355932204</v>
+        <v>0.7415254237288136</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3817307692307692</v>
+        <v>0.4241953385127636</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7040133779264214</v>
+        <v>0.7201773378698835</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5334183673469388</v>
+        <v>0.5623651010791914</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 3, 'model__p': 1, 'model__weights': 'distance'}</t>
+          <t>{'model__n_neighbors': 3, 'model__p': 1, 'model__weights': 'uniform'}</t>
         </is>
       </c>
     </row>
@@ -495,22 +495,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6652542372881356</v>
+        <v>0.5847457627118644</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8050847457627118</v>
+        <v>0.7669491525423728</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7966101694915254</v>
+        <v>0.7330508474576272</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2853061224489796</v>
+        <v>0.4318949001003558</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7038087962457711</v>
+        <v>0.6800354968324007</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4631279620853081</v>
+        <v>0.5912577319587629</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -528,23 +528,23 @@
         <v>0.652542372881356</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7796610169491526</v>
+        <v>0.7923728813559322</v>
       </c>
       <c r="D4" t="n">
         <v>0.7584745762711864</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2827868852459016</v>
+        <v>0.3236743838685586</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6793478260869565</v>
+        <v>0.6957402583734575</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4634438195524709</v>
+        <v>0.4915138915138915</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>{'model__max_depth': 10, 'model__max_features': 'sqrt', 'model__min_samples_leaf': 1, 'model__min_samples_split': 2, 'model__n_estimators': 200}</t>
+          <t>{'model__max_depth': 20, 'model__max_features': 'sqrt', 'model__min_samples_leaf': 1, 'model__min_samples_split': 2, 'model__n_estimators': 300}</t>
         </is>
       </c>
     </row>
@@ -588,23 +588,23 @@
         <v>0.5508474576271186</v>
       </c>
       <c r="C6" t="n">
-        <v>0.788135593220339</v>
+        <v>0.7923728813559322</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6864406779661016</v>
+        <v>0.6822033898305084</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5417735042735043</v>
+        <v>0.5424117866865958</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7501693766937669</v>
+        <v>0.7542032435649457</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6071974808816913</v>
+        <v>0.6037697835284637</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>{'model__estimator__C': 0.01, 'model__estimator__penalty': 'l1', 'model__estimator__solver': 'liblinear'}</t>
+          <t>{'model__estimator__C': 1, 'model__estimator__penalty': 'l1', 'model__estimator__solver': 'liblinear'}</t>
         </is>
       </c>
     </row>
@@ -615,26 +615,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5508474576271186</v>
+        <v>0.5466101694915254</v>
       </c>
       <c r="C7" t="n">
         <v>0.7923728813559322</v>
       </c>
       <c r="D7" t="n">
-        <v>0.690677966101695</v>
+        <v>0.6864406779661016</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5457255922372202</v>
+        <v>0.544055944055944</v>
       </c>
       <c r="F7" t="n">
         <v>0.7542032435649457</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6106402693967953</v>
+        <v>0.6071974808816913</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>{'model__estimator__alpha': 0.001, 'model__estimator__fit_intercept': True, 'model__estimator__solver': 'auto'}</t>
+          <t>{'model__estimator__alpha': 100, 'model__estimator__fit_intercept': True, 'model__estimator__solver': 'auto'}</t>
         </is>
       </c>
     </row>
@@ -645,22 +645,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5847457627118644</v>
+        <v>0.5508474576271186</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7330508474576272</v>
+        <v>0.7923728813559322</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6991525423728814</v>
+        <v>0.6779661016949152</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3395185079455705</v>
+        <v>0.5312967314676351</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6334952054625681</v>
+        <v>0.7614243568319201</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5246120237183307</v>
+        <v>0.5843529847979236</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -675,26 +675,26 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.652542372881356</v>
+        <v>0.6271186440677966</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7754237288135594</v>
+        <v>0.809322033898305</v>
       </c>
       <c r="D9" t="n">
-        <v>0.788135593220339</v>
+        <v>0.7542372881355932</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3411441499676794</v>
+        <v>0.4932891911238367</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6392374030169305</v>
+        <v>0.7576172543649435</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5704717530576587</v>
+        <v>0.5949337121212122</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>{'model__max_depth': 5, 'model__max_features': 'sqrt', 'model__min_samples_leaf': 4, 'model__min_samples_split': 10, 'model__n_estimators': 200}</t>
+          <t>{'model__max_depth': 5, 'model__max_features': 'sqrt', 'model__min_samples_leaf': 1, 'model__min_samples_split': 10, 'model__n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -705,26 +705,26 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.673728813559322</v>
+        <v>0.6440677966101694</v>
       </c>
       <c r="C10" t="n">
         <v>0.8050847457627118</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7711864406779662</v>
+        <v>0.7415254237288136</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3515531660692951</v>
+        <v>0.3492686890574215</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7238502238502238</v>
+        <v>0.7163461538461539</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4986624704956727</v>
+        <v>0.4943626848372028</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>{'model__estimator__learning_rate': 0.05, 'model__estimator__max_depth': 3, 'model__estimator__n_estimators': 200, 'model__estimator__subsample': 1.0}</t>
+          <t>{'model__estimator__learning_rate': 0.1, 'model__estimator__max_depth': 3, 'model__estimator__n_estimators': 200, 'model__estimator__subsample': 0.8}</t>
         </is>
       </c>
     </row>
@@ -735,26 +735,26 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4406779661016949</v>
+        <v>0.5423728813559322</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7584745762711864</v>
+        <v>0.7796610169491526</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5423728813559322</v>
+        <v>0.6779661016949152</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4294367050272562</v>
+        <v>0.5340390203403902</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6929818555289284</v>
+        <v>0.7421632069921842</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4829600778967867</v>
+        <v>0.6003565062388592</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>{'model__estimator__alpha': 0.001, 'model__estimator__loss': 'log_loss', 'model__estimator__penalty': 'elasticnet'}</t>
+          <t>{'model__estimator__alpha': 0.01, 'model__estimator__loss': 'log_loss', 'model__estimator__penalty': 'elasticnet'}</t>
         </is>
       </c>
     </row>
